--- a/TestCase_bai5.xlsx
+++ b/TestCase_bai5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hoc\kiemthu\app\tuan05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FC70B5-5AB2-4414-9D78-9FB18727A0BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08DE2EE-B27F-47B0-9E20-246985F46D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC_01" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="93">
   <si>
     <t>Test Case Description:</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t>27/1/26</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass </t>
   </si>
 </sst>
 </file>
@@ -382,18 +388,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -708,7 +713,8 @@
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="7" width="22" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
+    <col min="4" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -845,8 +851,6 @@
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -909,7 +913,9 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="22" customWidth="1"/>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" customWidth="1"/>
+    <col min="4" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1023,7 +1029,9 @@
         <v>38</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -1036,7 +1044,9 @@
         <v>40</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1052,7 +1062,9 @@
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="22" customWidth="1"/>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1103,7 +1115,7 @@
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -1176,7 +1188,9 @@
         <v>47</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -1189,7 +1203,9 @@
         <v>47</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1202,7 +1218,9 @@
         <v>50</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="E18" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1218,7 +1236,10 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1341,7 +1362,9 @@
         <v>56</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -1354,7 +1377,9 @@
         <v>58</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1370,7 +1395,9 @@
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="22" customWidth="1"/>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
+    <col min="4" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1421,7 +1448,7 @@
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -1494,7 +1521,9 @@
         <v>65</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -1507,7 +1536,9 @@
         <v>47</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1520,7 +1551,9 @@
         <v>68</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="E18" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1536,7 +1569,10 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" customWidth="1"/>
+    <col min="4" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1653,7 +1689,9 @@
         <v>73</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1669,7 +1707,10 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1777,7 +1818,9 @@
         <v>78</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1793,26 +1836,29 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="49.28515625" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" customWidth="1"/>
+    <col min="4" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="7"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="7"/>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="6"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1901,7 +1947,9 @@
         <v>82</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2027,7 +2075,9 @@
         <v>87</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -2040,7 +2090,9 @@
         <v>89</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
